--- a/PTBR/Lang/PTBR/Game/Block.xlsx
+++ b/PTBR/Lang/PTBR/Game/Block.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H207"/>
+  <dimension ref="A1:H216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -6047,6 +6047,249 @@
         </is>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>EA 23.283</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>bloco de nuvem</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>cloud block</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>雲のブロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EA 23.286</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>bloco alienígena</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>alien block</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>エイリアンのブロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>EA 23.288</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>bloco alienígena</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>alien block</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>エイリアンのブロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>parede alienígena</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>alien wall</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>エイリアンの壁</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>parede alienígena</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>alien wall</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>エイリアンの壁</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>parede alienígena</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>alien wall</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>エイリアンの壁</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>pilar alienígena</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>alien pillar</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>エイリアンの柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>pilar alienígena</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>alien pillar</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>エイリアンの柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>pilar alienígena</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>alien pillar</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>エイリアンの柱</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PTBR/Lang/PTBR/Game/Block.xlsx
+++ b/PTBR/Lang/PTBR/Game/Block.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H216"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -6047,249 +6047,6 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>EA 23.283</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>bloco de nuvem</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>cloud block</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>雲のブロック</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>EA 23.286</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>bloco alienígena</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>alien block</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>エイリアンのブロック</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>EA 23.288</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>bloco alienígena</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>alien block</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>エイリアンのブロック</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>EA 23.289</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>parede alienígena</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>alien wall</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>エイリアンの壁</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>EA 23.289</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>parede alienígena</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>alien wall</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>エイリアンの壁</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>EA 23.289</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>parede alienígena</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>alien wall</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>エイリアンの壁</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>EA 23.289</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>pilar alienígena</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>alien pillar</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>エイリアンの柱</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>EA 23.289</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>pilar alienígena</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>alien pillar</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>エイリアンの柱</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>EA 23.289</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>pilar alienígena</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>alien pillar</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>エイリアンの柱</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
